--- a/Comparaison du nombre de tours.xlsx
+++ b/Comparaison du nombre de tours.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Axel\Documents\Cours\sem 2\SAE\2 exploration algo\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3E2E95B-A55D-4396-8F39-1525F85DD633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31149374-9337-44BE-8238-C46C3D9769AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{31B572AB-9EFA-4904-B7F0-45C5E1F75AE5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>TEST 1</t>
   </si>
@@ -80,7 +80,40 @@
     <t>Flèches à partir d'un PP</t>
   </si>
   <si>
-    <t>TOTAL DU NOMBRE DE TOURS</t>
+    <t>TEST 11</t>
+  </si>
+  <si>
+    <t>TEST 12</t>
+  </si>
+  <si>
+    <t>TEST 13</t>
+  </si>
+  <si>
+    <t>TEST 14</t>
+  </si>
+  <si>
+    <t>TEST 15</t>
+  </si>
+  <si>
+    <t>TEST 16</t>
+  </si>
+  <si>
+    <t>TEST 17</t>
+  </si>
+  <si>
+    <t>TEST 18</t>
+  </si>
+  <si>
+    <t>TEST 19</t>
+  </si>
+  <si>
+    <t>TEST 20</t>
+  </si>
+  <si>
+    <t>Nombre de tours total</t>
+  </si>
+  <si>
+    <t>Nombre de tour pour :</t>
   </si>
 </sst>
 </file>
@@ -102,12 +135,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,8 +161,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,28 +498,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CE3EB0B-DEDB-4E30-ADB5-258FF5E690B6}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2">
@@ -493,7 +536,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
@@ -507,7 +550,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
@@ -521,7 +564,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
@@ -535,7 +578,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6">
@@ -549,7 +592,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7">
@@ -563,7 +606,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8">
@@ -577,7 +620,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9">
@@ -591,7 +634,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10">
@@ -605,7 +648,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11">
@@ -618,21 +661,161 @@
         <v>6</v>
       </c>
     </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>13</v>
+      <c r="A13" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B13">
-        <f>SUM(B2:B11)</f>
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <f>SUM(C2:C11)</f>
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <f>SUM(D2:D11)</f>
-        <v>52</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <f>SUM(B2:B21)</f>
+        <v>117</v>
+      </c>
+      <c r="C23">
+        <f>SUM(C2:C21)</f>
+        <v>108</v>
+      </c>
+      <c r="D23">
+        <f t="shared" ref="D23" si="0">SUM(D2:D21)</f>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
